--- a/exports/SUZLON_full_report.xlsx
+++ b/exports/SUZLON_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.56</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>10.75</v>
+        <v>10.2</v>
       </c>
       <c r="I2" t="n">
         <v>10.63536597253602</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>4.88</v>
+        <v>-0.49</v>
       </c>
       <c r="L2" t="n">
         <v>3.41</v>
@@ -555,7 +578,7 @@
         <v>2.68</v>
       </c>
       <c r="N2" t="n">
-        <v>4.91</v>
+        <v>5.12</v>
       </c>
       <c r="O2" t="n">
         <v>4.59</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>18.4</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.38541666666</v>
+        <v>44593.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>10.9</v>
+        <v>11.35</v>
       </c>
       <c r="I3" t="n">
         <v>11.23037530819467</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.86</v>
+        <v>-11.27</v>
       </c>
       <c r="L3" t="n">
         <v>12.75</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>14.96</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44600.38541666666</v>
+        <v>44600.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>9.783875512048626</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>-13.66</v>
+        <v>-14.54</v>
       </c>
       <c r="L4" t="n">
         <v>14.54</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>12.11</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44623.38541666666</v>
+        <v>44623.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>9.1</v>
+        <v>9.15</v>
       </c>
       <c r="I5" t="n">
         <v>9.116124585257538</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>22.83333333333333</v>
+        <v>23</v>
       </c>
       <c r="K5" t="n">
-        <v>6.19</v>
+        <v>5.67</v>
       </c>
       <c r="L5" t="n">
         <v>4.12</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>10.87</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44645.55208333334</v>
+        <v>44648.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>8.65</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>8.467163347574397</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>22</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.46</v>
+        <v>-7.65</v>
       </c>
       <c r="L6" t="n">
-        <v>7.1</v>
+        <v>8.74</v>
       </c>
       <c r="M6" t="n">
         <v>3.23</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>8.06</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44652.55208333334</v>
+        <v>44655.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I7" t="n">
         <v>8.988283379174565</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.14</v>
+        <v>-7.69</v>
       </c>
       <c r="L7" t="n">
-        <v>4.14</v>
+        <v>7.69</v>
       </c>
       <c r="M7" t="n">
         <v>1.18</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44662.55208333334</v>
+        <v>44663.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
         <v>10.01449672768498</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>13.19</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>2.75</v>
       </c>
       <c r="M8" t="n">
-        <v>0.47</v>
+        <v>1.94</v>
       </c>
       <c r="N8" t="n">
         <v>5.94</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>13.53</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44712.38541666666</v>
+        <v>44712.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>7.4</v>
+        <v>7.95</v>
       </c>
       <c r="I9" t="n">
         <v>7.875688573272308</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>20.5</v>
       </c>
       <c r="L9" t="n">
         <v>7.5</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>17.69</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44715.55208333334</v>
+        <v>44718.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>8.35</v>
+        <v>7.6</v>
       </c>
       <c r="I10" t="n">
         <v>7.759306869284589</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>5.03</v>
+        <v>-4.4</v>
       </c>
       <c r="L10" t="n">
         <v>7.55</v>
       </c>
       <c r="M10" t="n">
-        <v>0.61</v>
+        <v>1.2</v>
       </c>
       <c r="N10" t="n">
-        <v>7.22</v>
+        <v>8.98</v>
       </c>
       <c r="O10" t="n">
         <v>8.9</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>23.5</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44771.38541666666</v>
+        <v>44771.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>5.75</v>
+        <v>6.15</v>
       </c>
       <c r="I11" t="n">
         <v>6.112914580209715</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>53</v>
+        <v>53.16666666666666</v>
       </c>
       <c r="K11" t="n">
-        <v>24.34</v>
+        <v>19.08</v>
       </c>
       <c r="L11" t="n">
         <v>9.869999999999999</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>12.84</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44818.38541666666</v>
+        <v>44818.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>8.6</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>8.500850499555137</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>46.83333333333334</v>
+        <v>47</v>
       </c>
       <c r="K12" t="n">
-        <v>39.84</v>
+        <v>37.4</v>
       </c>
       <c r="L12" t="n">
         <v>6.5</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>14.51</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44826.38541666666</v>
+        <v>44826.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>8.550000000000001</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
         <v>8.749214363527773</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.18</v>
+        <v>-6.51</v>
       </c>
       <c r="L13" t="n">
-        <v>4.14</v>
+        <v>7.1</v>
       </c>
       <c r="M13" t="n">
         <v>0.62</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>16.32</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44832.38541666666</v>
+        <v>44832.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>7.55</v>
+        <v>7.5</v>
       </c>
       <c r="I14" t="n">
         <v>7.531636365542504</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>-16.11</v>
+        <v>-16.67</v>
       </c>
       <c r="L14" t="n">
         <v>18.89</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>16.01</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44851.55208333334</v>
+        <v>44852.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>7.45</v>
+        <v>7.8</v>
       </c>
       <c r="I15" t="n">
         <v>7.622183087652589</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>0.67</v>
+        <v>-4</v>
       </c>
       <c r="L15" t="n">
         <v>10</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>14.8</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44916.55208333334</v>
+        <v>44917.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>10.25</v>
+        <v>9.9</v>
       </c>
       <c r="I16" t="n">
         <v>10.21129143741026</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>64.16666666666667</v>
+        <v>65</v>
       </c>
       <c r="K16" t="n">
-        <v>31.41</v>
+        <v>26.92</v>
       </c>
       <c r="L16" t="n">
         <v>3.21</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>22.09</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45014.38541666666</v>
+        <v>45014.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>7.65</v>
+        <v>8.1</v>
       </c>
       <c r="I17" t="n">
         <v>7.706436237384957</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>97</v>
+        <v>97.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>22.73</v>
+        <v>18.18</v>
       </c>
       <c r="L17" t="n">
         <v>11.11</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>14.25</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45132.55208333334</v>
+        <v>45133.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>19</v>
+        <v>18.05</v>
       </c>
       <c r="I18" t="n">
         <v>18.57564949471124</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>118</v>
+        <v>118.8333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>134.57</v>
+        <v>122.84</v>
       </c>
       <c r="L18" t="n">
         <v>6.79</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
         <v>6.62</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>157</v>
+        <v>158</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>11.56</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45147.55208333334</v>
+        <v>45148.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>19.5</v>
+        <v>20.45</v>
       </c>
       <c r="I19" t="n">
         <v>19.69491597414924</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K19" t="n">
-        <v>-8.029999999999999</v>
+        <v>-13.3</v>
       </c>
       <c r="L19" t="n">
-        <v>9.970000000000001</v>
+        <v>13.3</v>
       </c>
       <c r="M19" t="n">
         <v>3.17</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.73</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45173.55208333334</v>
+        <v>45174.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>24.5</v>
+        <v>23.8</v>
       </c>
       <c r="I20" t="n">
         <v>23.97015665584567</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K20" t="n">
-        <v>19.8</v>
+        <v>16.38</v>
       </c>
       <c r="L20" t="n">
         <v>5.62</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>13.79</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45184.38541666666</v>
+        <v>45184.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>23.7</v>
+        <v>24.4</v>
       </c>
       <c r="I21" t="n">
         <v>24.33066682970524</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>0.42</v>
+        <v>-2.52</v>
       </c>
       <c r="L21" t="n">
         <v>4.83</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,25 +1937,25 @@
         <v>11.75</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45208.55208333334</v>
+        <v>45209.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>27.65</v>
+        <v>26.4</v>
       </c>
       <c r="I22" t="n">
         <v>27.22930286334647</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>13.32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L22" t="n">
         <v>3.69</v>
       </c>
       <c r="M22" t="n">
-        <v>3.59</v>
+        <v>4.16</v>
       </c>
       <c r="N22" t="n">
         <v>5.47</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>11.28</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45215.55208333334</v>
+        <v>45216.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>28.1</v>
+        <v>29.5</v>
       </c>
       <c r="I23" t="n">
         <v>28.73397933200029</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.44</v>
+        <v>-11.74</v>
       </c>
       <c r="L23" t="n">
-        <v>8.33</v>
+        <v>11.74</v>
       </c>
       <c r="M23" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="N23" t="n">
-        <v>4.54</v>
+        <v>4.98</v>
       </c>
       <c r="O23" t="n">
         <v>-4.34</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>9.25</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45250.55208333334</v>
+        <v>45251.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>41.2</v>
+        <v>39.3</v>
       </c>
       <c r="I24" t="n">
         <v>39.86285472653921</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K24" t="n">
-        <v>39.66</v>
+        <v>33.22</v>
       </c>
       <c r="L24" t="n">
         <v>2.88</v>
@@ -1809,7 +2096,7 @@
         <v>1.42</v>
       </c>
       <c r="N24" t="n">
-        <v>3.92</v>
+        <v>4.61</v>
       </c>
       <c r="O24" t="n">
         <v>4.98</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>14.75</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45296.38541666666</v>
+        <v>45296.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>39.4</v>
+        <v>40.6</v>
       </c>
       <c r="I25" t="n">
         <v>39.58871497281958</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>45</v>
+        <v>45.16666666666666</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.25</v>
+        <v>-3.31</v>
       </c>
       <c r="L25" t="n">
         <v>6.11</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>8.16</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45307.55208333334</v>
+        <v>45308.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>42.2</v>
+        <v>41.05</v>
       </c>
       <c r="I26" t="n">
         <v>41.23931854783713</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>3.94</v>
+        <v>1.11</v>
       </c>
       <c r="L26" t="n">
         <v>3.2</v>
       </c>
       <c r="M26" t="n">
-        <v>0.13</v>
+        <v>1.66</v>
       </c>
       <c r="N26" t="n">
         <v>3.98</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>11.27</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45321.55208333334</v>
+        <v>45322.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>44</v>
+        <v>45.4</v>
       </c>
       <c r="I27" t="n">
         <v>45.19827223661889</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.19</v>
+        <v>-10.6</v>
       </c>
       <c r="L27" t="n">
-        <v>9.26</v>
+        <v>10.84</v>
       </c>
       <c r="M27" t="n">
         <v>1.4</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.28</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45331.55208333334</v>
+        <v>45334.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>47.7</v>
+        <v>45</v>
       </c>
       <c r="I28" t="n">
         <v>45.50319324541423</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>5.07</v>
+        <v>-0.88</v>
       </c>
       <c r="L28" t="n">
         <v>2.64</v>
@@ -2037,7 +2372,7 @@
         <v>0.1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.34</v>
+        <v>5.66</v>
       </c>
       <c r="O28" t="n">
         <v>4.43</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>13.6</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45379.55208333334</v>
+        <v>45383.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>40.4</v>
+        <v>41.65</v>
       </c>
       <c r="I29" t="n">
         <v>40.63442460879733</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K29" t="n">
-        <v>10.22</v>
+        <v>7.44</v>
       </c>
       <c r="L29" t="n">
         <v>7.11</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>14.08</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45401.38541666666</v>
+        <v>45401.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>40.55</v>
+        <v>39.1</v>
       </c>
       <c r="I30" t="n">
         <v>40.28193179631514</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.64</v>
+        <v>-6.12</v>
       </c>
       <c r="L30" t="n">
         <v>7.8</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>10.86</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45427.38541666666</v>
+        <v>45427.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>41.55</v>
+        <v>42.2</v>
       </c>
       <c r="I31" t="n">
         <v>41.6653098197084</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>25.83333333333333</v>
+        <v>26</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.27</v>
+        <v>-7.93</v>
       </c>
       <c r="L31" t="n">
         <v>8.699999999999999</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.98</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45439.55208333334</v>
+        <v>45440.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>45.15</v>
+        <v>44.15</v>
       </c>
       <c r="I32" t="n">
         <v>44.48347867791032</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>6.99</v>
+        <v>4.62</v>
       </c>
       <c r="L32" t="n">
         <v>1.66</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>10.85</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>47.65</v>
+        <v>50</v>
       </c>
       <c r="I33" t="n">
         <v>48.23189317548074</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K33" t="n">
-        <v>-7.93</v>
+        <v>-13.25</v>
       </c>
       <c r="L33" t="n">
-        <v>7.93</v>
+        <v>13.25</v>
       </c>
       <c r="M33" t="n">
-        <v>0.78</v>
+        <v>4.93</v>
       </c>
       <c r="N33" t="n">
-        <v>4.73</v>
+        <v>4.93</v>
       </c>
       <c r="O33" t="n">
         <v>-2.1</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>9.34</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45534.38541666666</v>
+        <v>45534.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>76.15000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="I34" t="n">
         <v>75.88044755905693</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>88</v>
+        <v>88.16666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>52.3</v>
+        <v>51.4</v>
       </c>
       <c r="L34" t="n">
         <v>9.699999999999999</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>7.58</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45545.55208333334</v>
+        <v>45546.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>78.05</v>
+        <v>81.95</v>
       </c>
       <c r="I35" t="n">
         <v>79.18403520888108</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.1</v>
+        <v>-8.26</v>
       </c>
       <c r="L35" t="n">
-        <v>3.1</v>
+        <v>8.26</v>
       </c>
       <c r="M35" t="n">
         <v>2.04</v>
       </c>
       <c r="N35" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="O35" t="n">
         <v>-1.94</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>9.57</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>79.84999999999999</v>
+        <v>76.22</v>
       </c>
       <c r="I36" t="n">
         <v>78.22177991683625</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.56</v>
+        <v>-6.99</v>
       </c>
       <c r="L36" t="n">
-        <v>4.82</v>
+        <v>7.05</v>
       </c>
       <c r="M36" t="n">
-        <v>0.31</v>
+        <v>3.89</v>
       </c>
       <c r="N36" t="n">
-        <v>3.05</v>
+        <v>5.08</v>
       </c>
       <c r="O36" t="n">
         <v>5</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>8.4</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45573.55208333334</v>
+        <v>45574.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>73.88</v>
+        <v>77.48</v>
       </c>
       <c r="I37" t="n">
         <v>76.9104786822314</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K37" t="n">
-        <v>3.07</v>
+        <v>-1.65</v>
       </c>
       <c r="L37" t="n">
-        <v>3.12</v>
+        <v>5.75</v>
       </c>
       <c r="M37" t="n">
         <v>1.2</v>
       </c>
       <c r="N37" t="n">
-        <v>4.16</v>
+        <v>4.36</v>
       </c>
       <c r="O37" t="n">
         <v>-5.08</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>11.27</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>70.59</v>
+        <v>68.3</v>
       </c>
       <c r="I38" t="n">
         <v>69.36989897780592</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K38" t="n">
-        <v>-8.890000000000001</v>
+        <v>-11.85</v>
       </c>
       <c r="L38" t="n">
-        <v>9.01</v>
+        <v>12.88</v>
       </c>
       <c r="M38" t="n">
         <v>0.27</v>
       </c>
       <c r="N38" t="n">
-        <v>2.46</v>
+        <v>2.96</v>
       </c>
       <c r="O38" t="n">
         <v>4.36</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>10.47</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45614.55208333334</v>
+        <v>45615.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>59.1</v>
+        <v>62.22</v>
       </c>
       <c r="I39" t="n">
         <v>61.58148859183741</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K39" t="n">
-        <v>13.47</v>
+        <v>8.9</v>
       </c>
       <c r="L39" t="n">
         <v>7.61</v>
@@ -2664,7 +3131,7 @@
         <v>4.79</v>
       </c>
       <c r="N39" t="n">
-        <v>5.01</v>
+        <v>5.28</v>
       </c>
       <c r="O39" t="n">
         <v>-2.96</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>13.06</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45646.38541666666</v>
+        <v>45646.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>65.3</v>
+        <v>64.28</v>
       </c>
       <c r="I40" t="n">
         <v>64.9732218375392</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>4.95</v>
+        <v>3.31</v>
       </c>
       <c r="L40" t="n">
         <v>4.5</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45686.55208333334</v>
+        <v>45687.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>52.77</v>
+        <v>55.4</v>
       </c>
       <c r="I41" t="n">
         <v>55.19495290030032</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>40</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K41" t="n">
-        <v>17.91</v>
+        <v>13.81</v>
       </c>
       <c r="L41" t="n">
         <v>1.87</v>
       </c>
       <c r="M41" t="n">
-        <v>4.79</v>
+        <v>4.98</v>
       </c>
       <c r="N41" t="n">
         <v>5.21</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45694.55208333334</v>
+        <v>45695.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>54.99</v>
+        <v>53.87</v>
       </c>
       <c r="I42" t="n">
         <v>54.19852666955367</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.74</v>
+        <v>-2.76</v>
       </c>
       <c r="L42" t="n">
-        <v>1.53</v>
+        <v>3.5</v>
       </c>
       <c r="M42" t="n">
         <v>0.84</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>9.34</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45708.55208333334</v>
+        <v>45709.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>54.8</v>
+        <v>55.9</v>
       </c>
       <c r="I43" t="n">
         <v>55.46599197750675</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.73</v>
+        <v>-3.77</v>
       </c>
       <c r="L43" t="n">
-        <v>2.75</v>
+        <v>4.51</v>
       </c>
       <c r="M43" t="n">
         <v>0.68</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>10.72</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45715.55208333334</v>
+        <v>45716.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>52.02</v>
+        <v>49.77</v>
       </c>
       <c r="I44" t="n">
         <v>49.98850208984582</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K44" t="n">
-        <v>-6.94</v>
+        <v>-10.97</v>
       </c>
       <c r="L44" t="n">
-        <v>7.42</v>
+        <v>11.27</v>
       </c>
       <c r="M44" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.56</v>
       </c>
       <c r="N44" t="n">
         <v>4.23</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>11.97</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45722.55208333334</v>
+        <v>45723.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>51.9</v>
+        <v>54.92</v>
       </c>
       <c r="I45" t="n">
         <v>54.54205160096693</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.28</v>
+        <v>-10.35</v>
       </c>
       <c r="L45" t="n">
-        <v>6.27</v>
+        <v>14.41</v>
       </c>
       <c r="M45" t="n">
         <v>2.07</v>
       </c>
       <c r="N45" t="n">
-        <v>3.1</v>
+        <v>6.34</v>
       </c>
       <c r="O45" t="n">
         <v>-4.19</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>12.4</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>55.4</v>
+        <v>50.96</v>
       </c>
       <c r="I46" t="n">
         <v>53.63257392652434</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K46" t="n">
-        <v>0.87</v>
+        <v>-7.21</v>
       </c>
       <c r="L46" t="n">
-        <v>6.05</v>
+        <v>15.97</v>
       </c>
       <c r="M46" t="n">
-        <v>1.94</v>
+        <v>15.34</v>
       </c>
       <c r="N46" t="n">
-        <v>3.88</v>
+        <v>4.69</v>
       </c>
       <c r="O46" t="n">
         <v>6.34</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45764.55208333334</v>
+        <v>45768.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>55.1</v>
+        <v>58.75</v>
       </c>
       <c r="I47" t="n">
         <v>55.91563171957696</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K47" t="n">
-        <v>-8.119999999999999</v>
+        <v>-15.29</v>
       </c>
       <c r="L47" t="n">
-        <v>9.34</v>
+        <v>17.15</v>
       </c>
       <c r="M47" t="n">
         <v>5.31</v>
       </c>
       <c r="N47" t="n">
-        <v>3.63</v>
+        <v>9.49</v>
       </c>
       <c r="O47" t="n">
         <v>-4.69</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>11.24</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45782.55208333334</v>
+        <v>45783.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>56.98</v>
+        <v>55.29</v>
       </c>
       <c r="I48" t="n">
         <v>55.52821694286104</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.01</v>
+        <v>-5.89</v>
       </c>
       <c r="L48" t="n">
-        <v>5.53</v>
+        <v>6.37</v>
       </c>
       <c r="M48" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>3.47</v>
+        <v>5.58</v>
       </c>
       <c r="O48" t="n">
         <v>9.49</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>9.09</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45786.55208333334</v>
+        <v>45789.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>52.97</v>
+        <v>57.22</v>
       </c>
       <c r="I49" t="n">
         <v>56.81477317866605</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K49" t="n">
-        <v>4.2</v>
+        <v>-3.49</v>
       </c>
       <c r="L49" t="n">
         <v>3.98</v>
       </c>
       <c r="M49" t="n">
-        <v>1.09</v>
+        <v>6.17</v>
       </c>
       <c r="N49" t="n">
-        <v>2.04</v>
+        <v>7.85</v>
       </c>
       <c r="O49" t="n">
         <v>-5.58</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>11.22</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45820.38541666666</v>
+        <v>45820.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>66.15000000000001</v>
+        <v>65.72</v>
       </c>
       <c r="I50" t="n">
         <v>65.89992882594484</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>15.61</v>
+        <v>14.85</v>
       </c>
       <c r="L50" t="n">
         <v>3.46</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>6.93</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45834.55208333334</v>
+        <v>45835.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>64.64</v>
+        <v>66.42</v>
       </c>
       <c r="I51" t="n">
         <v>66.41847976354057</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>1.64</v>
+        <v>-1.07</v>
       </c>
       <c r="L51" t="n">
-        <v>0.73</v>
+        <v>1.17</v>
       </c>
       <c r="M51" t="n">
         <v>1.42</v>
       </c>
       <c r="N51" t="n">
-        <v>2.64</v>
+        <v>4.32</v>
       </c>
       <c r="O51" t="n">
         <v>-2.88</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>7.09</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45862.55208333334</v>
+        <v>45863.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>65.29000000000001</v>
+        <v>63.57</v>
       </c>
       <c r="I52" t="n">
         <v>64.77690956987139</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.7</v>
+        <v>-4.29</v>
       </c>
       <c r="L52" t="n">
-        <v>3.04</v>
+        <v>5.4</v>
       </c>
       <c r="M52" t="n">
         <v>0.6</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>5.59</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45869.55208333334</v>
+        <v>45870.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>61.47</v>
+        <v>65.55</v>
       </c>
       <c r="I53" t="n">
         <v>63.81233234262418</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K53" t="n">
-        <v>3.3</v>
+        <v>-3.11</v>
       </c>
       <c r="L53" t="n">
-        <v>2.75</v>
+        <v>3.81</v>
       </c>
       <c r="M53" t="n">
-        <v>0.03</v>
+        <v>1.35</v>
       </c>
       <c r="N53" t="n">
-        <v>1.71</v>
+        <v>7.21</v>
       </c>
       <c r="O53" t="n">
         <v>-2.37</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45881.55208333334</v>
+        <v>45882.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>63.22</v>
+        <v>60.51</v>
       </c>
       <c r="I54" t="n">
         <v>61.78461472222697</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.55</v>
+        <v>-7.69</v>
       </c>
       <c r="L54" t="n">
-        <v>5.1</v>
+        <v>8.31</v>
       </c>
       <c r="M54" t="n">
         <v>0.49</v>
       </c>
       <c r="N54" t="n">
-        <v>1.6</v>
+        <v>4.56</v>
       </c>
       <c r="O54" t="n">
         <v>7.21</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>10.81</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45917.38541666666</v>
+        <v>45917.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>59.2</v>
+        <v>59.27</v>
       </c>
       <c r="I55" t="n">
         <v>59.23467335436374</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K55" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="L55" t="n">
         <v>5.44</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>4.25</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45923.55208333334</v>
+        <v>45924.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>58.79</v>
+        <v>58.13</v>
       </c>
       <c r="I56" t="n">
         <v>58.17580842581813</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.92</v>
       </c>
       <c r="L56" t="n">
-        <v>1.08</v>
+        <v>2.4</v>
       </c>
       <c r="M56" t="n">
         <v>0.33</v>
       </c>
       <c r="N56" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="O56" t="n">
         <v>0.41</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>4.79</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45957.55208333334</v>
+        <v>45958.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>53.71</v>
+        <v>55.63</v>
       </c>
       <c r="I57" t="n">
         <v>55.26794389403446</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K57" t="n">
-        <v>7.6</v>
+        <v>4.3</v>
       </c>
       <c r="L57" t="n">
         <v>1.29</v>
@@ -3690,7 +4373,7 @@
         <v>0.83</v>
       </c>
       <c r="N57" t="n">
-        <v>2.16</v>
+        <v>4.82</v>
       </c>
       <c r="O57" t="n">
         <v>-2.13</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.39</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45979.55208333334</v>
+        <v>45980.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>56.8</v>
+        <v>56.55</v>
       </c>
       <c r="I58" t="n">
         <v>56.73734241173599</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K58" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="L58" t="n">
         <v>3.65</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>4.77</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>52.65</v>
+        <v>53.48</v>
       </c>
       <c r="I59" t="n">
         <v>53.45634580877775</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K59" t="n">
-        <v>6.9</v>
+        <v>5.43</v>
       </c>
       <c r="L59" t="n">
         <v>1.06</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>4.58</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46020.55208333334</v>
+        <v>46021.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>52.73</v>
+        <v>52.09</v>
       </c>
       <c r="I60" t="n">
         <v>52.09563900599537</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.4</v>
+        <v>-2.6</v>
       </c>
       <c r="L60" t="n">
-        <v>1.63</v>
+        <v>2.86</v>
       </c>
       <c r="M60" t="n">
         <v>0.04</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>4.85</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46024.38541666666</v>
+        <v>46024.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>54.03</v>
+        <v>54.29</v>
       </c>
       <c r="I61" t="n">
         <v>54.15438816641333</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.72</v>
+        <v>-4.22</v>
       </c>
       <c r="L61" t="n">
-        <v>4.09</v>
+        <v>4.43</v>
       </c>
       <c r="M61" t="n">
         <v>0.06</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>4.62</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46029.55208333334</v>
+        <v>46030.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>52.99</v>
+        <v>51.64</v>
       </c>
       <c r="I62" t="n">
         <v>51.77913425345313</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.39</v>
+        <v>-4.88</v>
       </c>
       <c r="L62" t="n">
-        <v>2.98</v>
+        <v>5.51</v>
       </c>
       <c r="M62" t="n">
         <v>0.19</v>
       </c>
       <c r="N62" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="O62" t="n">
         <v>3.29</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>6.55</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>47.15</v>
+        <v>48.96</v>
       </c>
       <c r="I63" t="n">
         <v>48.62398153043778</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K63" t="n">
-        <v>8.69</v>
+        <v>5.19</v>
       </c>
       <c r="L63" t="n">
         <v>3.43</v>
       </c>
       <c r="M63" t="n">
-        <v>1.42</v>
+        <v>4.58</v>
       </c>
       <c r="N63" t="n">
-        <v>3.92</v>
+        <v>4.54</v>
       </c>
       <c r="O63" t="n">
         <v>-4.1</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,25 +4835,25 @@
         <v>8.1</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46065.55208333334</v>
+        <v>46066.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>46.82</v>
+        <v>46.05</v>
       </c>
       <c r="I64" t="n">
         <v>46.21250847728824</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K64" t="n">
-        <v>-4.37</v>
+        <v>-5.94</v>
       </c>
       <c r="L64" t="n">
-        <v>4.62</v>
+        <v>6.29</v>
       </c>
       <c r="M64" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="N64" t="n">
         <v>4.1</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.41</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46092.55208333334</v>
+        <v>46093.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>41.67</v>
+        <v>43.22</v>
       </c>
       <c r="I65" t="n">
         <v>42.19416925550947</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K65" t="n">
-        <v>9.51</v>
+        <v>6.15</v>
       </c>
       <c r="L65" t="n">
         <v>1.5</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>10.34</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46147.55208333334</v>
+        <v>46148.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>54.92</v>
+        <v>53.48</v>
       </c>
       <c r="I66" t="n">
         <v>53.72583701362211</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K66" t="n">
-        <v>27.07</v>
+        <v>23.74</v>
       </c>
       <c r="L66" t="n">
         <v>9.529999999999999</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>8.85</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46169.38541666666</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>54.67</v>
+        <v>57.75</v>
       </c>
       <c r="I67" t="n">
         <v>55.64791710797439</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.23</v>
+        <v>-7.98</v>
       </c>
       <c r="L67" t="n">
-        <v>4.56</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="M67" t="n">
         <v>1.58</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>9.74</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46206.55208333334</v>
+        <v>46209.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>56.9</v>
+        <v>55.4</v>
       </c>
       <c r="I68" t="n">
         <v>55.81733374038444</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>37</v>
+        <v>39.83333333333334</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.47</v>
+        <v>-4.07</v>
       </c>
       <c r="L68" t="n">
         <v>8.99</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>7.15</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46304.55208333334</v>
+        <v>46307.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>37.6</v>
+        <v>39.64</v>
       </c>
       <c r="I69" t="n">
         <v>38.84000302728676</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>95.16666666666667</v>
+        <v>98</v>
       </c>
       <c r="K69" t="n">
-        <v>32.13</v>
+        <v>28.45</v>
       </c>
       <c r="L69" t="n">
         <v>3.07</v>
@@ -4374,7 +5201,7 @@
         <v>2.61</v>
       </c>
       <c r="N69" t="n">
-        <v>3.62</v>
+        <v>4.97</v>
       </c>
       <c r="O69" t="n">
         <v>-2.64</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>4</v>
+      </c>
+      <c r="U69" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -4410,25 +5249,25 @@
         <v>8.42</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46316.55208333334</v>
+        <v>46317.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>39.4</v>
+        <v>38.6</v>
       </c>
       <c r="I70" t="n">
         <v>38.69299925349209</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.61</v>
+        <v>-2.62</v>
       </c>
       <c r="L70" t="n">
         <v>3.76</v>
       </c>
       <c r="M70" t="n">
-        <v>0.4</v>
+        <v>0.89</v>
       </c>
       <c r="N70" t="n">
         <v>2.45</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,12 @@
       <c r="Q71" t="n">
         <v>8</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7450,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.2</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7460,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7470,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>118</v>
+        <v>118.8</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7480,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7490,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7500,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -6653,7 +7510,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -6663,7 +7520,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -6673,7 +7530,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>72.5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14">
@@ -6683,7 +7540,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.87</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7550,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.84</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7560,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.81</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7570,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>134.57</v>
+        <v>122.84</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7580,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.6</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7590,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.6</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7600,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.62</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="21">
@@ -6763,7 +7620,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
@@ -6773,7 +7630,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -6783,7 +7640,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.98</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="25">
@@ -6793,7 +7650,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12.85</v>
+        <v>15.34</v>
       </c>
     </row>
     <row r="26">
@@ -6803,7 +7660,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.81</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="27">
@@ -6823,7 +7680,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29">
